--- a/payroll/2026/excel/20260918-0919.xlsx
+++ b/payroll/2026/excel/20260918-0919.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\personal\cqsj\payroll\2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F02690-E7CD-4FF2-B6E6-83A05522FE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E10A021-4D26-4BC4-A8D9-4250061E8BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
+    <workbookView xWindow="7695" yWindow="1395" windowWidth="32145" windowHeight="19335" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
   </bookViews>
   <sheets>
     <sheet name="产出" sheetId="4" r:id="rId1"/>
@@ -292,9 +292,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0918-0919 集体产出 xxx ( 实际分配 xxx ) 行会账户A 往期结存 ( 4128 + 168 - 500 (行会库存石头因市场价格走低产生损失) = 3796)</t>
-  </si>
-  <si>
     <t>如意吉祥</t>
   </si>
   <si>
@@ -308,6 +305,117 @@
   </si>
   <si>
     <t>合计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">0918-0919 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集体产出</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 13658 ( </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>实际分配</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 13575 )  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行会账户</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>往期结存</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ( 4128 + 168 - 500 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.8"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行会库存石头因市场价格走低产生损失</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="19.8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) = 3796)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -315,7 +423,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,6 +511,14 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="19.8"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -495,67 +611,17 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1143,19 +1209,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
+      <c r="B1" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
     </row>
     <row r="2" spans="2:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
@@ -1309,7 +1375,7 @@
     </row>
     <row r="7" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="0"/>
@@ -1552,7 +1618,7 @@
     </row>
     <row r="16" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="0"/>
@@ -2058,7 +2124,7 @@
     </row>
     <row r="34" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="4">
         <f t="shared" si="0"/>
@@ -2121,7 +2187,7 @@
     </row>
     <row r="37" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" s="4">
         <f t="shared" si="0"/>
@@ -2164,8 +2230,8 @@
       <c r="M38" s="4"/>
     </row>
     <row r="39" spans="2:13" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="13" t="s">
-        <v>85</v>
+      <c r="B39" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="C39" s="4">
         <v>13575</v>
@@ -2176,15 +2242,13 @@
     <mergeCell ref="B1:L1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B40:B1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B40:B1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/payroll/2026/excel/20260918-0919.xlsx
+++ b/payroll/2026/excel/20260918-0919.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\personal\cqsj\payroll\2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E10A021-4D26-4BC4-A8D9-4250061E8BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896969B8-81C3-464D-9086-579B4CBCC407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7695" yWindow="1395" windowWidth="32145" windowHeight="19335" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
   </bookViews>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C19" s="4">
         <f t="shared" si="0"/>
-        <v>410</v>
+        <v>688</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4">
@@ -1727,7 +1727,9 @@
       <c r="I19" s="4">
         <v>43</v>
       </c>
-      <c r="J19" s="4"/>
+      <c r="J19" s="4">
+        <v>278</v>
+      </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4">
         <v>12</v>
@@ -1740,7 +1742,7 @@
       </c>
       <c r="C20" s="4">
         <f t="shared" si="0"/>
-        <v>327</v>
+        <v>49</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4">
@@ -1750,9 +1752,7 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="4">
-        <v>278</v>
-      </c>
+      <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
